--- a/results/feature_selection/global_ind/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/qP/metrics_global.xlsx
@@ -487,33 +487,33 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>X, V, P, T, I, mu, dXdt, dSdt, dVdt, Xlag1, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>V, P, T, I, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9570363774345253</v>
+        <v>0.9586278585202217</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00101154603915197</v>
+        <v>0.0009820246247765616</v>
       </c>
       <c r="F2" t="n">
-        <v>1.873664694464679e-06</v>
+        <v>1.804259422187337e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001368818722280156</v>
+        <v>0.001343227241455197</v>
       </c>
       <c r="H2" t="n">
-        <v>283.3728125361509</v>
+        <v>233.8776368007009</v>
       </c>
       <c r="I2" t="n">
-        <v>-681.7559443905335</v>
+        <v>-685.7187378250478</v>
       </c>
       <c r="J2" t="n">
-        <v>-677.8534569533706</v>
+        <v>-683.7674941064664</v>
       </c>
     </row>
     <row r="3">
@@ -523,33 +523,33 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>X, P, T, I, mu, dXdt, dSdt, dVdt, Xlag1, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>V, P, T, I, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9558027579983436</v>
+        <v>0.955954298995024</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00102846960345703</v>
+        <v>0.001028514785174635</v>
       </c>
       <c r="F3" t="n">
-        <v>1.92746344433631e-06</v>
+        <v>1.920854666996565e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001388331172428362</v>
+        <v>0.001385949013130196</v>
       </c>
       <c r="H3" t="n">
-        <v>226.0707933994308</v>
+        <v>229.3745341135649</v>
       </c>
       <c r="I3" t="n">
-        <v>-678.2838962447094</v>
+        <v>-682.4624972592615</v>
       </c>
       <c r="J3" t="n">
-        <v>-672.4301650889651</v>
+        <v>-680.5112535406801</v>
       </c>
     </row>
     <row r="4">
@@ -559,33 +559,33 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S, V, P, T, I, mu, dXdt, dSdt, dVdt, Xlag1, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>V, P, T, I, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.774713492621444</v>
+        <v>0.7746293484650832</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0020068378380331</v>
+        <v>0.002007409226085459</v>
       </c>
       <c r="F4" t="n">
-        <v>9.824855303371533e-06</v>
+        <v>9.828524871382895e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003134462522247081</v>
+        <v>0.003135047826012052</v>
       </c>
       <c r="H4" t="n">
-        <v>1076.502073781558</v>
+        <v>1077.697346997656</v>
       </c>
       <c r="I4" t="n">
-        <v>-595.5909466408996</v>
+        <v>-597.5715283487675</v>
       </c>
       <c r="J4" t="n">
-        <v>-591.6884592037367</v>
+        <v>-595.6202846301861</v>
       </c>
     </row>
     <row r="5">
@@ -627,73 +627,73 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P, T, dXdt, dXdt_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7186158847284428</v>
+        <v>0.7447039531697068</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002590078442450329</v>
+        <v>0.002158092905795912</v>
       </c>
       <c r="F6" t="n">
-        <v>1.227129955263983e-05</v>
+        <v>1.11335860669885e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003503041471727081</v>
+        <v>0.003336702873644655</v>
       </c>
       <c r="H6" t="n">
-        <v>1599.366766745576</v>
+        <v>697.2993394050822</v>
       </c>
       <c r="I6" t="n">
-        <v>-560.0288643756414</v>
+        <v>-575.0883008065431</v>
       </c>
       <c r="J6" t="n">
-        <v>-532.7114523155014</v>
+        <v>-557.5271073393102</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>V, P, Plag1, dXdt_calc</t>
+          <t>P, T, I, V_calc, mu_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.6412311024530613</v>
+        <v>0.7160850986659731</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002294778231121065</v>
+        <v>0.00261370813857913</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5646087938262e-05</v>
+        <v>1.238166837657376e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003955513612448073</v>
+        <v>0.003518759493994121</v>
       </c>
       <c r="H7" t="n">
-        <v>721.0681903958555</v>
+        <v>1602.566798539462</v>
       </c>
       <c r="I7" t="n">
-        <v>-547.3950614995625</v>
+        <v>-577.5632638682929</v>
       </c>
       <c r="J7" t="n">
-        <v>-520.0776494394225</v>
+        <v>-567.8070452753858</v>
       </c>
     </row>
     <row r="8">
@@ -703,33 +703,33 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>X, V, P, mu, dXdt, dVdt, Xlag1, Plag1, X_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>V, P, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.09880818468001751</v>
+        <v>-0.09934532660919149</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006248129167221733</v>
+        <v>0.006229286603128756</v>
       </c>
       <c r="F8" t="n">
-        <v>4.791956494092777e-05</v>
+        <v>4.794298996443634e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006922395895997842</v>
+        <v>0.006924087662965882</v>
       </c>
       <c r="H8" t="n">
-        <v>3914.436919242119</v>
+        <v>3994.87226872347</v>
       </c>
       <c r="I8" t="n">
-        <v>-505.1913075191409</v>
+        <v>-511.1658940248335</v>
       </c>
       <c r="J8" t="n">
-        <v>-493.4838452076523</v>
+        <v>-505.3121628690892</v>
       </c>
     </row>
     <row r="9">
@@ -739,33 +739,33 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>S, V, P, I, mu, dSdt, dVdt, Plag1, X_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>V, P, T, I, Xlag1_calc, Plag1, X_calc, mu_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.09951945285527963</v>
+        <v>-0.1088497527453474</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006280482540950996</v>
+        <v>0.006294030624682612</v>
       </c>
       <c r="F9" t="n">
-        <v>4.795058369560223e-05</v>
+        <v>4.835748265916486e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00692463599733605</v>
+        <v>0.00695395446197089</v>
       </c>
       <c r="H9" t="n">
-        <v>3911.315688563514</v>
+        <v>3988.301495834766</v>
       </c>
       <c r="I9" t="n">
-        <v>-493.1576583525901</v>
+        <v>-500.7182585638749</v>
       </c>
       <c r="J9" t="n">
-        <v>-469.742733729613</v>
+        <v>-485.1083088152234</v>
       </c>
     </row>
     <row r="10">
@@ -775,33 +775,33 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>X, S, V, P, T, I, mu, dXdt, dSdt, dVdt, Plag1, X_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>V, P, T, I, Xlag1_calc, Plag1, X_calc, mu_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.4992496115160339</v>
+        <v>-0.520284148951957</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007621610778201842</v>
+        <v>0.007679265232176601</v>
       </c>
       <c r="F10" t="n">
-        <v>6.538301236136563e-05</v>
+        <v>6.630033887632658e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008085976277566341</v>
+        <v>0.008142502003458554</v>
       </c>
       <c r="H10" t="n">
-        <v>4438.820000612738</v>
+        <v>4478.960013885682</v>
       </c>
       <c r="I10" t="n">
-        <v>-471.0329003195446</v>
+        <v>-484.3084085754928</v>
       </c>
       <c r="J10" t="n">
-        <v>-441.7642445408231</v>
+        <v>-468.6984588268414</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/qP/metrics_global.xlsx
@@ -487,33 +487,33 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>V, P, T, I, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc</t>
+          <t>X, V, P, T, I, mu, dXdt, dVdt, Xlag1, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9586278585202217</v>
+        <v>0.9567511892309655</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009820246247765616</v>
+        <v>0.001016377321300306</v>
       </c>
       <c r="F2" t="n">
-        <v>1.804259422187337e-06</v>
+        <v>1.886101892177081e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001343227241455197</v>
+        <v>0.001373354248610707</v>
       </c>
       <c r="H2" t="n">
-        <v>233.8776368007009</v>
+        <v>292.3921440369698</v>
       </c>
       <c r="I2" t="n">
-        <v>-685.7187378250478</v>
+        <v>-683.4119141827232</v>
       </c>
       <c r="J2" t="n">
-        <v>-683.7674941064664</v>
+        <v>-681.4606704641418</v>
       </c>
     </row>
     <row r="3">
@@ -523,33 +523,33 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>V, P, T, I, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc</t>
+          <t>X, P, T, I, mu, dXdt, dVdt, Xlag1, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.955954298995024</v>
+        <v>0.955841566549924</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001028514785174635</v>
+        <v>0.00102797137519596</v>
       </c>
       <c r="F3" t="n">
-        <v>1.920854666996565e-06</v>
+        <v>1.925770984329504e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001385949013130196</v>
+        <v>0.001387721508203106</v>
       </c>
       <c r="H3" t="n">
-        <v>229.3745341135649</v>
+        <v>225.9600398573359</v>
       </c>
       <c r="I3" t="n">
-        <v>-682.4624972592615</v>
+        <v>-680.3295762715247</v>
       </c>
       <c r="J3" t="n">
-        <v>-680.5112535406801</v>
+        <v>-676.4270888343618</v>
       </c>
     </row>
     <row r="4">
@@ -559,33 +559,33 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>V, P, T, I, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc</t>
+          <t>X, V, P, T, I, mu, dXdt, dVdt, Xlag1, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7746293484650832</v>
+        <v>0.7747265661010263</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002007409226085459</v>
+        <v>0.002006578793424306</v>
       </c>
       <c r="F4" t="n">
-        <v>9.828524871382895e-06</v>
+        <v>9.824285162502011e-06</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003135047826012052</v>
+        <v>0.003134371573777112</v>
       </c>
       <c r="H4" t="n">
-        <v>1077.697346997656</v>
+        <v>1075.923967189804</v>
       </c>
       <c r="I4" t="n">
-        <v>-597.5715283487675</v>
+        <v>-597.5939643123621</v>
       </c>
       <c r="J4" t="n">
-        <v>-595.6202846301861</v>
+        <v>-595.6427205937807</v>
       </c>
     </row>
     <row r="5">
@@ -639,25 +639,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7447039531697068</v>
+        <v>0.73821817442231</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002158092905795912</v>
+        <v>0.002161498412356386</v>
       </c>
       <c r="F6" t="n">
-        <v>1.11335860669885e-05</v>
+        <v>1.141643406558516e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003336702873644655</v>
+        <v>0.003378821401847863</v>
       </c>
       <c r="H6" t="n">
-        <v>697.2993394050822</v>
+        <v>681.041078875101</v>
       </c>
       <c r="I6" t="n">
-        <v>-575.0883008065431</v>
+        <v>-559.783746109351</v>
       </c>
       <c r="J6" t="n">
-        <v>-557.5271073393102</v>
+        <v>-528.5638466120481</v>
       </c>
     </row>
     <row r="7">
@@ -671,29 +671,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P, T, I, V_calc, mu_calc</t>
+          <t>P, T, dXdt, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7160850986659731</v>
+        <v>0.7193067722785886</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00261370813857913</v>
+        <v>0.002584443540921786</v>
       </c>
       <c r="F7" t="n">
-        <v>1.238166837657376e-05</v>
+        <v>1.22411696070427e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003518759493994121</v>
+        <v>0.003498738287875031</v>
       </c>
       <c r="H7" t="n">
-        <v>1602.566798539462</v>
+        <v>1595.731102948303</v>
       </c>
       <c r="I7" t="n">
-        <v>-577.5632638682929</v>
+        <v>-564.1566979243462</v>
       </c>
       <c r="J7" t="n">
-        <v>-567.8070452753858</v>
+        <v>-540.7417733013691</v>
       </c>
     </row>
     <row r="8">
@@ -703,33 +703,33 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>V, P, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc</t>
+          <t>X, V, P, mu, dXdt, dVdt, Xlag1, Xlag1_calc, Plag1, X_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.09934532660919149</v>
+        <v>-0.09628265318034845</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006229286603128756</v>
+        <v>0.00623443109460362</v>
       </c>
       <c r="F8" t="n">
-        <v>4.794298996443634e-05</v>
+        <v>4.780942527105991e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006924087662965882</v>
+        <v>0.006914436005276202</v>
       </c>
       <c r="H8" t="n">
-        <v>3994.87226872347</v>
+        <v>3917.609206778285</v>
       </c>
       <c r="I8" t="n">
-        <v>-511.1658940248335</v>
+        <v>-509.310963338085</v>
       </c>
       <c r="J8" t="n">
-        <v>-505.3121628690892</v>
+        <v>-501.5059884637593</v>
       </c>
     </row>
     <row r="9">
@@ -739,33 +739,33 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>V, P, T, I, Xlag1_calc, Plag1, X_calc, mu_calc</t>
+          <t>V, P, I, mu, dVdt, Plag1, X_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1088497527453474</v>
+        <v>-0.09951625270628583</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006294030624682612</v>
+        <v>0.006280485994865138</v>
       </c>
       <c r="F9" t="n">
-        <v>4.835748265916486e-05</v>
+        <v>4.795044413553191e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00695395446197089</v>
+        <v>0.006924625920259658</v>
       </c>
       <c r="H9" t="n">
-        <v>3988.301495834766</v>
+        <v>3911.300789243483</v>
       </c>
       <c r="I9" t="n">
-        <v>-500.7182585638749</v>
+        <v>-497.1578096986982</v>
       </c>
       <c r="J9" t="n">
-        <v>-485.1083088152234</v>
+        <v>-477.6453725128839</v>
       </c>
     </row>
     <row r="10">
@@ -775,33 +775,33 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>V, P, T, I, Xlag1_calc, Plag1, X_calc, mu_calc</t>
+          <t>X, V, P, T, I, mu, dXdt, dVdt, Xlag1_calc, Plag1, X_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.520284148951957</v>
+        <v>-0.4909157123444228</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007679265232176601</v>
+        <v>0.007596188317421902</v>
       </c>
       <c r="F10" t="n">
-        <v>6.630033887632658e-05</v>
+        <v>6.501956692281397e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008142502003458554</v>
+        <v>0.008063471146027247</v>
       </c>
       <c r="H10" t="n">
-        <v>4478.960013885682</v>
+        <v>4432.479127412804</v>
       </c>
       <c r="I10" t="n">
-        <v>-484.3084085754928</v>
+        <v>-473.3227597969342</v>
       </c>
       <c r="J10" t="n">
-        <v>-468.6984588268414</v>
+        <v>-446.0053477367942</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/qP/metrics_global.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,15 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>SCORE</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>AIC</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>BIC</t>
         </is>
@@ -487,33 +492,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>X, V, P, T, I, mu, dXdt, dVdt, Xlag1, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, mu, Plag1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9567511892309655</v>
+        <v>0.9508998674552321</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001016377321300306</v>
+        <v>0.001073433663888101</v>
       </c>
       <c r="F2" t="n">
-        <v>1.886101892177081e-06</v>
+        <v>2.141280644538669e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001373354248610707</v>
+        <v>0.001463311533658731</v>
       </c>
       <c r="H2" t="n">
-        <v>292.3921440369698</v>
+        <v>815748.9718621908</v>
       </c>
       <c r="I2" t="n">
-        <v>-683.4119141827232</v>
+        <v>0.01623153865988154</v>
       </c>
       <c r="J2" t="n">
-        <v>-681.4606704641418</v>
+        <v>-672.8135367463913</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-666.959805590647</v>
       </c>
     </row>
     <row r="3">
@@ -523,105 +531,114 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>X, P, T, I, mu, dXdt, dVdt, Xlag1, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, mu, Plag1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.955841566549924</v>
+        <v>0.948560954051039</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00102797137519596</v>
+        <v>0.001141310742638832</v>
       </c>
       <c r="F3" t="n">
-        <v>1.925770984329504e-06</v>
+        <v>2.243281794883519e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001387721508203106</v>
+        <v>0.001497758924154191</v>
       </c>
       <c r="H3" t="n">
-        <v>225.9600398573359</v>
+        <v>904363.6944071437</v>
       </c>
       <c r="I3" t="n">
-        <v>-680.3295762715247</v>
+        <v>0.01693328408194471</v>
       </c>
       <c r="J3" t="n">
-        <v>-676.4270888343618</v>
+        <v>-670.3936752190076</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-664.5399440632633</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>X, V, P, T, I, mu, dXdt, dVdt, Xlag1, Xlag1_calc, Plag1, X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7747265661010263</v>
+        <v>0.7669713421991845</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002006578793424306</v>
+        <v>0.002143934678532394</v>
       </c>
       <c r="F4" t="n">
-        <v>9.824285162502011e-06</v>
+        <v>1.016249302620026e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003134371573777112</v>
+        <v>0.00318786653205561</v>
       </c>
       <c r="H4" t="n">
-        <v>1075.923967189804</v>
+        <v>1257276.432572004</v>
       </c>
       <c r="I4" t="n">
-        <v>-597.5939643123621</v>
+        <v>0.070415711085363</v>
       </c>
       <c r="J4" t="n">
-        <v>-595.6427205937807</v>
+        <v>-595.8339520046055</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-593.8827082860241</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>V, P, Plag1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7669712942021927</v>
+        <v>0.7625989858801634</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002143935737371529</v>
+        <v>0.002083469846549938</v>
       </c>
       <c r="F5" t="n">
-        <v>1.016249638132264e-05</v>
+        <v>1.035317361038014e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003187867058288761</v>
+        <v>0.003217634785114703</v>
       </c>
       <c r="H5" t="n">
-        <v>767.9330127488606</v>
+        <v>2170334.043232618</v>
       </c>
       <c r="I5" t="n">
-        <v>-595.8339348369348</v>
+        <v>0.07272755145747826</v>
       </c>
       <c r="J5" t="n">
-        <v>-593.8826911183534</v>
+        <v>-590.86730772405</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-585.0135765683057</v>
       </c>
     </row>
     <row r="6">
@@ -639,25 +656,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.73821817442231</v>
+        <v>0.7382102864240997</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002161498412356386</v>
+        <v>0.002163558311531234</v>
       </c>
       <c r="F6" t="n">
-        <v>1.141643406558516e-05</v>
+        <v>1.141677664736023e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003378821401847863</v>
+        <v>0.00337887209692232</v>
       </c>
       <c r="H6" t="n">
-        <v>681.041078875101</v>
+        <v>1201280.784129658</v>
       </c>
       <c r="I6" t="n">
-        <v>-559.783746109351</v>
+        <v>0.07904490581642326</v>
       </c>
       <c r="J6" t="n">
-        <v>-528.5638466120481</v>
+        <v>-589.7821857285066</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-587.8309420099253</v>
       </c>
     </row>
     <row r="7">
@@ -667,33 +687,36 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P, T, dXdt, dXdt_calc, dVdt_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7193067722785886</v>
+        <v>0.7026639146396708</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002584443540921786</v>
+        <v>0.00265263693570824</v>
       </c>
       <c r="F7" t="n">
-        <v>1.22411696070427e-05</v>
+        <v>1.296697119757197e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003498738287875031</v>
+        <v>0.003600968091718111</v>
       </c>
       <c r="H7" t="n">
-        <v>1595.731102948303</v>
+        <v>2425016.35430729</v>
       </c>
       <c r="I7" t="n">
-        <v>-564.1566979243462</v>
+        <v>0.08970990248793706</v>
       </c>
       <c r="J7" t="n">
-        <v>-540.7417733013691</v>
+        <v>-583.1614657517115</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-581.2102220331301</v>
       </c>
     </row>
     <row r="8">
@@ -703,33 +726,36 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>X, V, P, mu, dXdt, dVdt, Xlag1, Xlag1_calc, Plag1, X_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.09628265318034845</v>
+        <v>-0.1242029088271321</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00623443109460362</v>
+        <v>0.006317828313126768</v>
       </c>
       <c r="F8" t="n">
-        <v>4.780942527105991e-05</v>
+        <v>4.902703525312839e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006914436005276202</v>
+        <v>0.007001930823217864</v>
       </c>
       <c r="H8" t="n">
-        <v>3917.609206778285</v>
+        <v>6447359.365153105</v>
       </c>
       <c r="I8" t="n">
-        <v>-509.310963338085</v>
+        <v>0.6765903831456338</v>
       </c>
       <c r="J8" t="n">
-        <v>-501.5059884637593</v>
+        <v>-512.0032109516106</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-508.1007235144478</v>
       </c>
     </row>
     <row r="9">
@@ -739,33 +765,36 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>V, P, I, mu, dVdt, Plag1, X_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.09951625270628583</v>
+        <v>-0.1414033683926041</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006280485994865138</v>
+        <v>0.006397569769799989</v>
       </c>
       <c r="F9" t="n">
-        <v>4.795044413553191e-05</v>
+        <v>4.977715565476141e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006924625920259658</v>
+        <v>0.007055292740543188</v>
       </c>
       <c r="H9" t="n">
-        <v>3911.300789243483</v>
+        <v>6483728.30712072</v>
       </c>
       <c r="I9" t="n">
-        <v>-497.1578096986982</v>
+        <v>0.6869117090534792</v>
       </c>
       <c r="J9" t="n">
-        <v>-477.6453725128839</v>
+        <v>-511.213628850473</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-507.3111414133102</v>
       </c>
     </row>
     <row r="10">
@@ -775,33 +804,36 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>X, V, P, T, I, mu, dXdt, dVdt, Xlag1_calc, Plag1, X_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.4909157123444228</v>
+        <v>-0.669484385513847</v>
       </c>
       <c r="E10" t="n">
-        <v>0.007596188317421902</v>
+        <v>0.008015256809686643</v>
       </c>
       <c r="F10" t="n">
-        <v>6.501956692281397e-05</v>
+        <v>7.280702547596839e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008063471146027247</v>
+        <v>0.008532703292390307</v>
       </c>
       <c r="H10" t="n">
-        <v>4432.479127412804</v>
+        <v>7503434.920505269</v>
       </c>
       <c r="I10" t="n">
-        <v>-473.3227597969342</v>
+        <v>1.002792561143975</v>
       </c>
       <c r="J10" t="n">
-        <v>-446.0053477367942</v>
+        <v>-493.4403013886067</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-491.4890576700252</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/qP/metrics_global.xlsx
@@ -488,280 +488,280 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P, mu, Plag1</t>
+          <t>T, X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9508998674552321</v>
+        <v>0.4280516651750005</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001073433663888101</v>
+        <v>0.002627054897657552</v>
       </c>
       <c r="F2" t="n">
-        <v>2.141280644538669e-06</v>
+        <v>2.494294796455613e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001463311533658731</v>
+        <v>0.004994291537801546</v>
       </c>
       <c r="H2" t="n">
-        <v>815748.9718621908</v>
+        <v>243.1624140259625</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01623153865988154</v>
+        <v>0.1736019605110751</v>
       </c>
       <c r="J2" t="n">
-        <v>-672.8135367463913</v>
+        <v>-543.1438099663617</v>
       </c>
       <c r="K2" t="n">
-        <v>-666.959805590647</v>
+        <v>-535.338835092036</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P, mu, Plag1</t>
+          <t>X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.948560954051039</v>
+        <v>0.2355958930041859</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001141310742638832</v>
+        <v>0.002868888387211934</v>
       </c>
       <c r="F3" t="n">
-        <v>2.243281794883519e-06</v>
+        <v>3.333603877092048e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001497758924154191</v>
+        <v>0.005773736984910248</v>
       </c>
       <c r="H3" t="n">
-        <v>904363.6944071437</v>
+        <v>645.654313999945</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01693328408194471</v>
+        <v>0.2318445673258839</v>
       </c>
       <c r="J3" t="n">
-        <v>-670.3936752190076</v>
+        <v>-526.0613180421318</v>
       </c>
       <c r="K3" t="n">
-        <v>-664.5399440632633</v>
+        <v>-516.3050994492247</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>T, X_calc, V_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7669713421991845</v>
+        <v>0.2038909854354329</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002143934678532394</v>
+        <v>0.002848281689172955</v>
       </c>
       <c r="F4" t="n">
-        <v>1.016249302620026e-05</v>
+        <v>3.471870537130569e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00318786653205561</v>
+        <v>0.005892258087635477</v>
       </c>
       <c r="H4" t="n">
-        <v>1257276.432572004</v>
+        <v>459.3704510836642</v>
       </c>
       <c r="I4" t="n">
-        <v>0.070415711085363</v>
+        <v>0.2403570074631301</v>
       </c>
       <c r="J4" t="n">
-        <v>-595.8339520046055</v>
+        <v>-527.948061741127</v>
       </c>
       <c r="K4" t="n">
-        <v>-593.8827082860241</v>
+        <v>-522.0943305853827</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>V, P, Plag1</t>
+          <t>T, X_calc, V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7625989858801634</v>
+        <v>0.1697881749854229</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002083469846549938</v>
+        <v>0.004431078090678579</v>
       </c>
       <c r="F5" t="n">
-        <v>1.035317361038014e-05</v>
+        <v>3.620594569478699e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003217634785114703</v>
+        <v>0.006017137666265164</v>
       </c>
       <c r="H5" t="n">
-        <v>2170334.043232618</v>
+        <v>1292.992110584417</v>
       </c>
       <c r="I5" t="n">
-        <v>0.07272755145747826</v>
+        <v>0.2510888916663595</v>
       </c>
       <c r="J5" t="n">
-        <v>-590.86730772405</v>
+        <v>-523.7669347591666</v>
       </c>
       <c r="K5" t="n">
-        <v>-585.0135765683057</v>
+        <v>-515.9619598848409</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.7382102864240997</v>
+        <v>0.09115459594013675</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002163558311531234</v>
+        <v>0.003007672759483949</v>
       </c>
       <c r="F6" t="n">
-        <v>1.141677664736023e-05</v>
+        <v>3.963519472126331e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00337887209692232</v>
+        <v>0.00629564887213886</v>
       </c>
       <c r="H6" t="n">
-        <v>1201280.784129658</v>
+        <v>720.2022924471084</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07904490581642326</v>
+        <v>0.2736813658542639</v>
       </c>
       <c r="J6" t="n">
-        <v>-589.7821857285066</v>
+        <v>-523.0612400989405</v>
       </c>
       <c r="K6" t="n">
-        <v>-587.8309420099253</v>
+        <v>-519.1587526617776</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.7026639146396708</v>
+        <v>-0.09021998986335711</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00265263693570824</v>
+        <v>0.005924024099798451</v>
       </c>
       <c r="F7" t="n">
-        <v>1.296697119757197e-05</v>
+        <v>4.754502954432244e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003600968091718111</v>
+        <v>0.006895290388687227</v>
       </c>
       <c r="H7" t="n">
-        <v>2425016.35430729</v>
+        <v>3305.99305674323</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08970990248793706</v>
+        <v>0.6561985569593765</v>
       </c>
       <c r="J7" t="n">
-        <v>-583.1614657517115</v>
+        <v>-513.5993318899529</v>
       </c>
       <c r="K7" t="n">
-        <v>-581.2102220331301</v>
+        <v>-509.69684445279</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>T, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1242029088271321</v>
+        <v>-0.09422135154509115</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006317828313126768</v>
+        <v>0.003369351027859656</v>
       </c>
       <c r="F8" t="n">
-        <v>4.902703525312839e-05</v>
+        <v>4.771953089372387e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007001930823217864</v>
+        <v>0.006907932461578057</v>
       </c>
       <c r="H8" t="n">
-        <v>6447359.365153105</v>
+        <v>642.3181412946305</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6765903831456338</v>
+        <v>0.661599618270306</v>
       </c>
       <c r="J8" t="n">
-        <v>-512.0032109516106</v>
+        <v>-507.4088291410608</v>
       </c>
       <c r="K8" t="n">
-        <v>-508.1007235144478</v>
+        <v>-497.6526105481536</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -769,38 +769,38 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P, Plag1</t>
+          <t>T, V_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1414033683926041</v>
+        <v>-0.102146659552691</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006397569769799989</v>
+        <v>0.005578211818958222</v>
       </c>
       <c r="F9" t="n">
-        <v>4.977715565476141e-05</v>
+        <v>4.806515747081169e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007055292740543188</v>
+        <v>0.006932903970978662</v>
       </c>
       <c r="H9" t="n">
-        <v>6483728.30712072</v>
+        <v>1051.828707017569</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6869117090534792</v>
+        <v>0.6633552869520738</v>
       </c>
       <c r="J9" t="n">
-        <v>-511.213628850473</v>
+        <v>-513.0335570528169</v>
       </c>
       <c r="K9" t="n">
-        <v>-507.3111414133102</v>
+        <v>-509.1310696156541</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -808,32 +808,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Xlag1_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.669484385513847</v>
+        <v>-0.1334676173115339</v>
       </c>
       <c r="E10" t="n">
-        <v>0.008015256809686643</v>
+        <v>0.003822479863718049</v>
       </c>
       <c r="F10" t="n">
-        <v>7.280702547596839e-05</v>
+        <v>4.943107983129538e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008532703292390307</v>
+        <v>0.007030723990550005</v>
       </c>
       <c r="H10" t="n">
-        <v>7503434.920505269</v>
+        <v>1416.601738920101</v>
       </c>
       <c r="I10" t="n">
-        <v>1.002792561143975</v>
+        <v>0.6811497738986843</v>
       </c>
       <c r="J10" t="n">
-        <v>-493.4403013886067</v>
+        <v>-513.5764216313107</v>
       </c>
       <c r="K10" t="n">
-        <v>-491.4890576700252</v>
+        <v>-511.6251779127293</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/qP/metrics_global.xlsx
@@ -500,28 +500,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4280516651750005</v>
+        <v>0.425158062775427</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002627054897657552</v>
+        <v>0.002614939507281203</v>
       </c>
       <c r="F2" t="n">
-        <v>2.494294796455613e-05</v>
+        <v>2.418457107672554e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004994291537801546</v>
+        <v>0.004917781113136853</v>
       </c>
       <c r="H2" t="n">
-        <v>243.1624140259625</v>
+        <v>237.743298724906</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1736019605110751</v>
+        <v>0.1744695103671256</v>
       </c>
       <c r="J2" t="n">
-        <v>-543.1438099663617</v>
+        <v>-566.0089670948504</v>
       </c>
       <c r="K2" t="n">
-        <v>-535.338835092036</v>
+        <v>-558.0530309085933</v>
       </c>
     </row>
     <row r="3">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2355958930041859</v>
+        <v>0.2381859035061848</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002868888387211934</v>
+        <v>0.00278829217006141</v>
       </c>
       <c r="F3" t="n">
-        <v>3.333603877092048e-05</v>
+        <v>3.205080557076401e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005773736984910248</v>
+        <v>0.005661343088946651</v>
       </c>
       <c r="H3" t="n">
-        <v>645.654313999945</v>
+        <v>623.2859236943095</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2318445673258839</v>
+        <v>0.2310666645120441</v>
       </c>
       <c r="J3" t="n">
-        <v>-526.0613180421318</v>
+        <v>-548.8021649654129</v>
       </c>
       <c r="K3" t="n">
-        <v>-516.3050994492247</v>
+        <v>-538.8572447325915</v>
       </c>
     </row>
     <row r="4">
@@ -570,36 +570,36 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2038909854354329</v>
+        <v>0.1714015906449656</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002848281689172955</v>
+        <v>0.002898652184346955</v>
       </c>
       <c r="F4" t="n">
-        <v>3.471870537130569e-05</v>
+        <v>3.486053439639672e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005892258087635477</v>
+        <v>0.005904281022816979</v>
       </c>
       <c r="H4" t="n">
-        <v>459.3704510836642</v>
+        <v>634.4388991882182</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2403570074631301</v>
+        <v>0.2496039251805878</v>
       </c>
       <c r="J4" t="n">
-        <v>-527.948061741127</v>
+        <v>-550.2643801629226</v>
       </c>
       <c r="K4" t="n">
-        <v>-522.0943305853827</v>
+        <v>-546.2864120697941</v>
       </c>
     </row>
     <row r="5">
@@ -609,36 +609,36 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc, Xlag1_calc</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1697881749854229</v>
+        <v>0.1204445775650165</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004431078090678579</v>
+        <v>0.005012717655867164</v>
       </c>
       <c r="F5" t="n">
-        <v>3.620594569478699e-05</v>
+        <v>3.700438199151088e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006017137666265164</v>
+        <v>0.00608312271711749</v>
       </c>
       <c r="H5" t="n">
-        <v>1292.992110584417</v>
+        <v>1720.380491525877</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2510888916663595</v>
+        <v>0.2648925297978892</v>
       </c>
       <c r="J5" t="n">
-        <v>-523.7669347591666</v>
+        <v>-547.041607886998</v>
       </c>
       <c r="K5" t="n">
-        <v>-515.9619598848409</v>
+        <v>-543.0636397938695</v>
       </c>
     </row>
     <row r="6">
@@ -656,112 +656,112 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.09115459594013675</v>
+        <v>0.08711683679443427</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003007672759483949</v>
+        <v>0.002959263133907777</v>
       </c>
       <c r="F6" t="n">
-        <v>3.963519472126331e-05</v>
+        <v>3.840653632872644e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00629564887213886</v>
+        <v>0.006197300729247084</v>
       </c>
       <c r="H6" t="n">
-        <v>720.2022924471084</v>
+        <v>712.8363906341297</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2736813658542639</v>
+        <v>0.2748918335370998</v>
       </c>
       <c r="J6" t="n">
-        <v>-523.0612400989405</v>
+        <v>-545.033276381944</v>
       </c>
       <c r="K6" t="n">
-        <v>-519.1587526617776</v>
+        <v>-541.0553082888155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>svm_linear</t>
+          <t>linear</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>Xlag1_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.09021998986335711</v>
+        <v>-0.1321230812480487</v>
       </c>
       <c r="E7" t="n">
-        <v>0.005924024099798451</v>
+        <v>0.003726334759176992</v>
       </c>
       <c r="F7" t="n">
-        <v>4.754502954432244e-05</v>
+        <v>4.763032992728307e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006895290388687227</v>
+        <v>0.006901473025904186</v>
       </c>
       <c r="H7" t="n">
-        <v>3305.99305674323</v>
+        <v>1345.416873877073</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6561985569593765</v>
+        <v>0.6803405312107276</v>
       </c>
       <c r="J7" t="n">
-        <v>-513.5993318899529</v>
+        <v>-535.4102040799696</v>
       </c>
       <c r="K7" t="n">
-        <v>-509.69684445279</v>
+        <v>-533.4212200334053</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>svm_linear</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T, V_calc, mu_calc, dXdt_calc, Xlag1_calc</t>
+          <t>V_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.09422135154509115</v>
+        <v>-0.1605346082033081</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003369351027859656</v>
+        <v>0.006095692521784973</v>
       </c>
       <c r="F8" t="n">
-        <v>4.771953089372387e-05</v>
+        <v>4.882565084691761e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006907932461578057</v>
+        <v>0.006987535391460827</v>
       </c>
       <c r="H8" t="n">
-        <v>642.3181412946305</v>
+        <v>3352.498448765714</v>
       </c>
       <c r="I8" t="n">
-        <v>0.661599618270306</v>
+        <v>0.6983891208331707</v>
       </c>
       <c r="J8" t="n">
-        <v>-507.4088291410608</v>
+        <v>-532.0717565589881</v>
       </c>
       <c r="K8" t="n">
-        <v>-497.6526105481536</v>
+        <v>-528.0937884658596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>svm_poly</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -769,71 +769,71 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T, V_calc</t>
+          <t>T, mu_calc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.102146659552691</v>
+        <v>-0.2327080674994608</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005578211818958222</v>
+        <v>0.003463190098808811</v>
       </c>
       <c r="F9" t="n">
-        <v>4.806515747081169e-05</v>
+        <v>5.186211016411432e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006932903970978662</v>
+        <v>0.007201535264380389</v>
       </c>
       <c r="H9" t="n">
-        <v>1051.828707017569</v>
+        <v>905.4147450301265</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6633552869520738</v>
+        <v>0.7416974474539063</v>
       </c>
       <c r="J9" t="n">
-        <v>-513.0335570528169</v>
+        <v>-528.8137928088855</v>
       </c>
       <c r="K9" t="n">
-        <v>-509.1310696156541</v>
+        <v>-524.835824715757</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>svm_poly</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xlag1_calc</t>
+          <t>T, V_calc, mu_calc, dXdt_calc</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.1334676173115339</v>
+        <v>-0.2780188423114556</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003822479863718049</v>
+        <v>0.006250414893965202</v>
       </c>
       <c r="F10" t="n">
-        <v>4.943107983129538e-05</v>
+        <v>5.376841098007947e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.007030723990550005</v>
+        <v>0.00733269466022413</v>
       </c>
       <c r="H10" t="n">
-        <v>1416.601738920101</v>
+        <v>2305.844420624398</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6811497738986843</v>
+        <v>0.7708865811622456</v>
       </c>
       <c r="J10" t="n">
-        <v>-513.5764216313107</v>
+        <v>-522.8645186662039</v>
       </c>
       <c r="K10" t="n">
-        <v>-511.6251779127293</v>
+        <v>-514.9085824799469</v>
       </c>
     </row>
   </sheetData>

--- a/results/feature_selection/global_ind/wnp/qP/metrics_global.xlsx
+++ b/results/feature_selection/global_ind/wnp/qP/metrics_global.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>knn</t>
+          <t>Ridge_w</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -496,188 +496,188 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>T, X_calc, V_calc, Xlag1_calc</t>
+          <t>P, Plag1, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.425158062775427</v>
+        <v>0.9559263753143085</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002614939507281203</v>
+        <v>0.0009973447489325289</v>
       </c>
       <c r="F2" t="n">
-        <v>2.418457107672554e-05</v>
+        <v>1.922072432435606e-06</v>
       </c>
       <c r="G2" t="n">
-        <v>0.004917781113136853</v>
+        <v>0.001386388269005334</v>
       </c>
       <c r="H2" t="n">
-        <v>237.743298724906</v>
+        <v>237.1821662911826</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1744695103671256</v>
+        <v>0.01522343285641017</v>
       </c>
       <c r="J2" t="n">
-        <v>-566.0089670948504</v>
+        <v>-676.4295412320919</v>
       </c>
       <c r="K2" t="n">
-        <v>-558.0530309085933</v>
+        <v>-668.6245663577662</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ridge_w</t>
+          <t>elasticnet_w</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>X_calc, V_calc, mu_calc, dXdt_calc, dVdt_calc</t>
+          <t>P, Plag1, dXdt_calc, Xlag1_calc</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2381859035061848</v>
+        <v>0.9530324409671134</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00278829217006141</v>
+        <v>0.001077999084994512</v>
       </c>
       <c r="F3" t="n">
-        <v>3.205080557076401e-05</v>
+        <v>2.048278331534893e-06</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005661343088946651</v>
+        <v>0.001431180747332388</v>
       </c>
       <c r="H3" t="n">
-        <v>623.2859236943095</v>
+        <v>305.0678319370571</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2310666645120441</v>
+        <v>0.01609170150469806</v>
       </c>
       <c r="J3" t="n">
-        <v>-548.8021649654129</v>
+        <v>-673.1225697094708</v>
       </c>
       <c r="K3" t="n">
-        <v>-538.8572447325915</v>
+        <v>-665.3175948351451</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>elasticnet_w</t>
+          <t>knn</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1714015906449656</v>
+        <v>0.7669712942021927</v>
       </c>
       <c r="E4" t="n">
-        <v>0.002898652184346955</v>
+        <v>0.002143935737371529</v>
       </c>
       <c r="F4" t="n">
-        <v>3.486053439639672e-05</v>
+        <v>1.016249638132264e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005904281022816979</v>
+        <v>0.003187867058288761</v>
       </c>
       <c r="H4" t="n">
-        <v>634.4388991882182</v>
+        <v>767.9330127488605</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2496039251805878</v>
+        <v>0.07041572548680913</v>
       </c>
       <c r="J4" t="n">
-        <v>-550.2643801629226</v>
+        <v>-595.8339348369348</v>
       </c>
       <c r="K4" t="n">
-        <v>-546.2864120697941</v>
+        <v>-593.8826911183534</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>svm_rbf</t>
+          <t>LASSO_w</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>P, Plag1, V_calc</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1204445775650165</v>
+        <v>0.7625393523897337</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005012717655867164</v>
+        <v>0.002052731799132868</v>
       </c>
       <c r="F5" t="n">
-        <v>3.700438199151088e-05</v>
+        <v>1.035577554183271e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00608312271711749</v>
+        <v>0.003218039083328962</v>
       </c>
       <c r="H5" t="n">
-        <v>1720.380491525877</v>
+        <v>1185.602848199082</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2648925297978892</v>
+        <v>0.07274544332595918</v>
       </c>
       <c r="J5" t="n">
-        <v>-547.041607886998</v>
+        <v>-590.854240867277</v>
       </c>
       <c r="K5" t="n">
-        <v>-543.0636397938695</v>
+        <v>-585.0005097115327</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LASSO_w</t>
+          <t>rf_w</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.08711683679443427</v>
+        <v>0.7382102718309593</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002959263133907777</v>
+        <v>0.002163558968330788</v>
       </c>
       <c r="F6" t="n">
-        <v>3.840653632872644e-05</v>
+        <v>1.141677870147767e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006197300729247084</v>
+        <v>0.003378872400887265</v>
       </c>
       <c r="H6" t="n">
-        <v>712.8363906341297</v>
+        <v>712.1552046815564</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2748918335370998</v>
+        <v>0.07904491019580324</v>
       </c>
       <c r="J6" t="n">
-        <v>-545.033276381944</v>
+        <v>-589.7821763726175</v>
       </c>
       <c r="K6" t="n">
-        <v>-541.0553082888155</v>
+        <v>-587.8309326540361</v>
       </c>
     </row>
     <row r="7">
@@ -687,36 +687,36 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Xlag1_calc</t>
+          <t>P, dXdt_calc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.1321230812480487</v>
+        <v>0.7144448945554122</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003726334759176992</v>
+        <v>0.002575511495768102</v>
       </c>
       <c r="F7" t="n">
-        <v>4.763032992728307e-05</v>
+        <v>1.245319848391028e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006901473025904186</v>
+        <v>0.003528908965092508</v>
       </c>
       <c r="H7" t="n">
-        <v>1345.416873877073</v>
+        <v>1637.961606447373</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6803405312107276</v>
+        <v>0.08667524887231511</v>
       </c>
       <c r="J7" t="n">
-        <v>-535.4102040799696</v>
+        <v>-583.2637192089285</v>
       </c>
       <c r="K7" t="n">
-        <v>-533.4212200334053</v>
+        <v>-579.3612317717656</v>
       </c>
     </row>
     <row r="8">
@@ -730,38 +730,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>V_calc, Xlag1_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.1605346082033081</v>
+        <v>-0.1242002360157195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.006095692521784973</v>
+        <v>0.006317818528247028</v>
       </c>
       <c r="F8" t="n">
-        <v>4.882565084691761e-05</v>
+        <v>4.902692477854935e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.006987535391460827</v>
+        <v>0.007001922934348061</v>
       </c>
       <c r="H8" t="n">
-        <v>3352.498448765714</v>
+        <v>4084.153894534492</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6983891208331707</v>
+        <v>0.6765887793041218</v>
       </c>
       <c r="J8" t="n">
-        <v>-532.0717565589881</v>
+        <v>-512.0033281254219</v>
       </c>
       <c r="K8" t="n">
-        <v>-528.0937884658596</v>
+        <v>-508.1008406882591</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rf_w</t>
+          <t>svm_rbf</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -769,32 +769,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T, mu_calc</t>
+          <t>P, Plag1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.2327080674994608</v>
+        <v>-0.1414006598275086</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003463190098808811</v>
+        <v>0.00639756004483344</v>
       </c>
       <c r="F9" t="n">
-        <v>5.186211016411432e-05</v>
+        <v>4.977704371409454e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007201535264380389</v>
+        <v>0.007055284807440061</v>
       </c>
       <c r="H9" t="n">
-        <v>905.4147450301265</v>
+        <v>4104.803997347538</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7416974474539063</v>
+        <v>0.686910083757705</v>
       </c>
       <c r="J9" t="n">
-        <v>-528.8137928088855</v>
+        <v>-511.2137457900841</v>
       </c>
       <c r="K9" t="n">
-        <v>-524.835824715757</v>
+        <v>-507.3112583529212</v>
       </c>
     </row>
     <row r="10">
@@ -804,36 +804,36 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>T, V_calc, mu_calc, dXdt_calc</t>
+          <t>P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.2780188423114556</v>
+        <v>-0.6694811383557357</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006250414893965202</v>
+        <v>0.008015248454678674</v>
       </c>
       <c r="F10" t="n">
-        <v>5.376841098007947e-05</v>
+        <v>7.280689290678027e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00733269466022413</v>
+        <v>0.008532695524087348</v>
       </c>
       <c r="H10" t="n">
-        <v>2305.844420624398</v>
+        <v>4715.700996988844</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7708865811622456</v>
+        <v>1.002790612663511</v>
       </c>
       <c r="J10" t="n">
-        <v>-522.8645186662039</v>
+        <v>-493.4403960718328</v>
       </c>
       <c r="K10" t="n">
-        <v>-514.9085824799469</v>
+        <v>-491.4891523532514</v>
       </c>
     </row>
   </sheetData>
